--- a/reports/Debug-purgatory-20260106/For The Day (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Day (Actual)_Budget.xlsx
@@ -40,6 +40,39 @@
     <t>D8040</t>
   </si>
   <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5205</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
     <t>D1020</t>
   </si>
   <si>
@@ -55,37 +88,7 @@
     <t>D6215</t>
   </si>
   <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D4053</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5205</t>
-  </si>
-  <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>D6710</t>
-  </si>
-  <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>D8060</t>
+    <t>D6780</t>
   </si>
   <si>
     <t>D1030</t>
@@ -100,6 +103,12 @@
     <t>D5810</t>
   </si>
   <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -124,12 +133,6 @@
     <t>D6800</t>
   </si>
   <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
     <t>99100</t>
   </si>
   <si>
@@ -154,9 +157,6 @@
     <t>D8020</t>
   </si>
   <si>
-    <t>D6780</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -196,6 +196,39 @@
     <t>HR</t>
   </si>
   <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Expert Edge</t>
+  </si>
+  <si>
+    <t>Purg Sports Main Ave</t>
+  </si>
+  <si>
+    <t>Waffle Cabin</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
     <t>Lift Maintenance</t>
   </si>
   <si>
@@ -211,37 +244,7 @@
     <t>Housekeeping</t>
   </si>
   <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>Expert Edge</t>
-  </si>
-  <si>
-    <t>Purg Sports Main Ave</t>
-  </si>
-  <si>
-    <t>Waffle Cabin</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>Accounting/Mgmt Services</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>IT Services</t>
+    <t>Grounds Maintenance</t>
   </si>
   <si>
     <t>Snowmaking</t>
@@ -256,6 +259,12 @@
     <t>Events</t>
   </si>
   <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>Mountain G&amp;A</t>
   </si>
   <si>
@@ -280,12 +289,6 @@
     <t>Commercial Tenants</t>
   </si>
   <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
     <t>Daily Winter Ticketed</t>
   </si>
   <si>
@@ -308,9 +311,6 @@
   </si>
   <si>
     <t>Accounting</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="2">
-        <v>1780.56</v>
+        <v>3944.97</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>60</v>
@@ -830,7 +830,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="2">
-        <v>2383.57</v>
+        <v>1112.00</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>61</v>
@@ -844,7 +844,7 @@
         <v>49</v>
       </c>
       <c r="C12" s="2">
-        <v>594.37</v>
+        <v>3983.60</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>62</v>
@@ -855,10 +855,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2">
-        <v>34146.58</v>
+        <v>1006.39</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>63</v>
@@ -869,10 +869,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2">
-        <v>1657.84</v>
+        <v>174212.86</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>63</v>
@@ -886,7 +886,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>703.69</v>
+        <v>586.26</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>64</v>
@@ -900,7 +900,7 @@
         <v>50</v>
       </c>
       <c r="C16" s="2">
-        <v>15000.00</v>
+        <v>2388.74</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>64</v>
@@ -911,10 +911,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2">
-        <v>3944.97</v>
+        <v>3764.07</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>65</v>
@@ -922,156 +922,156 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="2">
-        <v>1112.00</v>
+        <v>649.76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>3983.60</v>
+        <v>169.03</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2">
-        <v>1006.39</v>
+        <v>963.60</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>174212.86</v>
+        <v>1424.78</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2">
-        <v>586.26</v>
+        <v>4206.82</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>2388.74</v>
+        <v>1190.63</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="2">
-        <v>3764.07</v>
+        <v>1745.45</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>649.76</v>
+        <v>1050.69</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2">
-        <v>169.03</v>
+        <v>1635.79</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2">
-        <v>963.60</v>
+        <v>849.62</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>1424.78</v>
+        <v>1780.56</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1079,10 +1079,10 @@
         <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>4206.82</v>
+        <v>2383.57</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>72</v>
@@ -1096,7 +1096,7 @@
         <v>49</v>
       </c>
       <c r="C30" s="2">
-        <v>1190.63</v>
+        <v>594.37</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>73</v>
@@ -1104,16 +1104,16 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C31" s="2">
-        <v>1745.45</v>
+        <v>34146.58</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1124,7 +1124,7 @@
         <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>1050.69</v>
+        <v>1657.84</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>74</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2">
-        <v>1635.79</v>
+        <v>703.69</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1149,10 +1149,10 @@
         <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" s="2">
-        <v>849.62</v>
+        <v>15000.00</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>75</v>
@@ -1163,10 +1163,10 @@
         <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2">
-        <v>236.90</v>
+        <v>376.71</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>76</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2">
-        <v>4076.80</v>
+        <v>1626.10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1194,7 +1194,7 @@
         <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>138.75</v>
+        <v>236.90</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>77</v>
@@ -1205,10 +1205,10 @@
         <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2">
-        <v>2661.10</v>
+        <v>4076.80</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>78</v>
@@ -1219,10 +1219,10 @@
         <v>26</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>12557.28</v>
+        <v>138.75</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>78</v>
@@ -1236,7 +1236,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="2">
-        <v>201.25</v>
+        <v>2661.10</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>79</v>
@@ -1250,7 +1250,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="2">
-        <v>0.00</v>
+        <v>12557.28</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>79</v>
@@ -1264,7 +1264,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="2">
-        <v>377.99</v>
+        <v>201.25</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>80</v>
@@ -1272,16 +1272,16 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2">
-        <v>579.26</v>
+        <v>0.00</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1289,10 +1289,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>11356.80</v>
+        <v>914.00</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>81</v>
@@ -1306,7 +1306,7 @@
         <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>569.90</v>
+        <v>227.21</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>82</v>
@@ -1314,142 +1314,142 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2">
-        <v>767.76</v>
+        <v>377.99</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>495.21</v>
+        <v>579.26</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="2">
-        <v>720.12</v>
+        <v>11356.80</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>391.37</v>
+        <v>569.90</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C50" s="2">
-        <v>1079.50</v>
+        <v>767.76</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="2">
-        <v>180.00</v>
+        <v>495.21</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="2">
-        <v>221.25</v>
+        <v>720.12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="2">
-        <v>790.25</v>
+        <v>391.37</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C54" s="2">
-        <v>863.28</v>
+        <v>1079.50</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2">
-        <v>0.00</v>
+        <v>180.00</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1457,10 +1457,10 @@
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C56" s="2">
-        <v>914.00</v>
+        <v>221.25</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>88</v>
@@ -1474,7 +1474,7 @@
         <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>227.21</v>
+        <v>790.25</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>89</v>
@@ -1482,30 +1482,30 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C58" s="2">
-        <v>1130.00</v>
+        <v>863.28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C59" s="2">
-        <v>6095.92</v>
+        <v>0.00</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1513,10 +1513,10 @@
         <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C60" s="2">
-        <v>26555.00</v>
+        <v>1130.00</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>91</v>
@@ -1530,7 +1530,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="2">
-        <v>266.97</v>
+        <v>6095.92</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>92</v>
@@ -1544,7 +1544,7 @@
         <v>50</v>
       </c>
       <c r="C62" s="2">
-        <v>614.25</v>
+        <v>26555.00</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>92</v>
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C63" s="2">
-        <v>28758.50</v>
+        <v>266.97</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>93</v>
@@ -1569,10 +1569,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C64" s="2">
-        <v>1585.50</v>
+        <v>614.25</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>93</v>
@@ -1586,7 +1586,7 @@
         <v>50</v>
       </c>
       <c r="C65" s="2">
-        <v>6559.84</v>
+        <v>28758.50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>94</v>
@@ -1600,7 +1600,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="2">
-        <v>2126.25</v>
+        <v>1585.50</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>94</v>
@@ -1614,7 +1614,7 @@
         <v>50</v>
       </c>
       <c r="C67" s="2">
-        <v>2139.92</v>
+        <v>6559.84</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>95</v>
@@ -1628,7 +1628,7 @@
         <v>49</v>
       </c>
       <c r="C68" s="2">
-        <v>321.50</v>
+        <v>2126.25</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>95</v>
@@ -1639,10 +1639,10 @@
         <v>44</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C69" s="2">
-        <v>642.47</v>
+        <v>2139.92</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>96</v>
@@ -1650,30 +1650,30 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C70" s="2">
-        <v>700.16</v>
+        <v>321.50</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C71" s="2">
-        <v>376.71</v>
+        <v>642.47</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1684,7 +1684,7 @@
         <v>49</v>
       </c>
       <c r="C72" s="2">
-        <v>1626.10</v>
+        <v>700.16</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
